--- a/VerveStacks_UZB_grids_kan15/SysSettings.xlsx
+++ b/VerveStacks_UZB_grids_kan15/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_UZB_grids_kan15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2AC28A-968F-411B-969D-1F98359D8EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67AAA428-50D3-445B-AD6F-8BAC1E4926B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -3587,15 +3587,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.53125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -3652,9 +3652,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93467CAE-E9B9-4E4D-9EAD-DAF9FB060E12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F526DED9-C4FE-41C4-A3D3-5C9C69AFE987}">
   <dimension ref="B3:I19"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
@@ -4083,9 +4083,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{384008FA-6211-4E47-BB66-68333A8EF3F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB447BA-EA0C-4B18-8772-AEEB0711368B}">
   <dimension ref="B3:I19"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
@@ -4516,19 +4516,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:S53"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:19" ht="17.25" thickBot="1">
+    <row r="3" spans="2:19" ht="18" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -4547,7 +4547,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:19" ht="15" thickTop="1" thickBot="1">
+    <row r="4" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="30" spans="2:19" ht="17.25" thickBot="1">
+    <row r="30" spans="2:19" ht="18" thickBot="1">
       <c r="B30" s="3" t="s">
         <v>212</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="15" thickTop="1" thickBot="1">
+    <row r="31" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
       <c r="B31" s="5" t="s">
         <v>172</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="38" spans="2:19" ht="17.25" thickBot="1">
+    <row r="38" spans="2:19" ht="18" thickBot="1">
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="39" spans="2:19" ht="15" thickTop="1" thickBot="1">
+    <row r="39" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
       <c r="B39" s="5" t="s">
         <v>218</v>
       </c>
@@ -6117,15 +6117,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="6"/>
-    <col min="4" max="4" width="14.1328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="6"/>
+    <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="6"/>
+    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -6156,7 +6156,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.25">
+    <row r="12" spans="2:7" ht="15">
       <c r="B12" s="7" t="s">
         <v>42</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14.25">
+    <row r="13" spans="2:7" ht="15">
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14.25">
+    <row r="14" spans="2:7" ht="15">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14.25">
+    <row r="15" spans="2:7" ht="15">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14.25">
+    <row r="16" spans="2:7" ht="15">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14.25">
+    <row r="17" spans="2:7" ht="15">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14.25">
+    <row r="18" spans="2:7" ht="15">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.25">
+    <row r="19" spans="2:7" ht="15">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.25">
+    <row r="20" spans="2:7" ht="15">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.25">
+    <row r="21" spans="2:7" ht="15">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.25">
+    <row r="22" spans="2:7" ht="15">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.25">
+    <row r="23" spans="2:7" ht="15">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.25">
+    <row r="24" spans="2:7" ht="15">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -6344,46 +6344,46 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.25">
+    <row r="25" spans="2:7" ht="15">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.25">
+    <row r="26" spans="2:7" ht="15">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.25">
+    <row r="27" spans="2:7" ht="15">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.25">
+    <row r="28" spans="2:7" ht="15">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.25">
+    <row r="29" spans="2:7" ht="15">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.25">
+    <row r="30" spans="2:7" ht="15">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="14.25">
+    <row r="31" spans="2:7" ht="15">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="14.25">
+    <row r="32" spans="2:7" ht="15">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" ht="14.25">
+    <row r="33" spans="2:2" ht="15">
       <c r="B33" s="9"/>
     </row>
   </sheetData>
@@ -6395,21 +6395,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="8.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.46484375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.46484375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.53125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.3984375" style="11"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="12.75">
@@ -6641,7 +6641,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="14.25">
+    <row r="21" spans="2:14" ht="15">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -6656,7 +6656,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25">
+    <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -6671,7 +6671,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="14.25">
+    <row r="23" spans="2:14" ht="15">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -6686,7 +6686,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="14.25">
+    <row r="24" spans="2:14" ht="15">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -6701,7 +6701,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="14.25">
+    <row r="25" spans="2:14" ht="15">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -6716,7 +6716,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="14.25">
+    <row r="26" spans="2:14" ht="15">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -6731,7 +6731,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="14.25">
+    <row r="27" spans="2:14" ht="15">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -6746,7 +6746,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="14.25">
+    <row r="28" spans="2:14" ht="15">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -6761,7 +6761,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="14.25">
+    <row r="29" spans="2:14" ht="15">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -6776,7 +6776,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="14.25">
+    <row r="30" spans="2:14" ht="15">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -6791,7 +6791,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="14.25">
+    <row r="31" spans="2:14" ht="15">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -6806,7 +6806,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="14.25">
+    <row r="32" spans="2:14" ht="15">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -6821,7 +6821,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="14.25">
+    <row r="33" spans="2:14" ht="15">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -6836,7 +6836,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="14.25">
+    <row r="34" spans="2:14" ht="15">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -6851,7 +6851,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="14.25">
+    <row r="35" spans="2:14" ht="15">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -6866,7 +6866,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="14.25">
+    <row r="36" spans="2:14" ht="15">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -6881,7 +6881,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="14.25">
+    <row r="37" spans="2:14" ht="15">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -6896,7 +6896,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="14.25">
+    <row r="38" spans="2:14" ht="15">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -6911,7 +6911,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="14.25">
+    <row r="39" spans="2:14" ht="15">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -6926,7 +6926,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="14.25">
+    <row r="40" spans="2:14" ht="15">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -6941,7 +6941,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="14.25">
+    <row r="41" spans="2:14" ht="15">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -6956,7 +6956,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="14.25">
+    <row r="42" spans="2:14" ht="15">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -6981,25 +6981,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="12.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.3984375" style="11"/>
-    <col min="5" max="5" width="13.53125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.3984375" style="11"/>
-    <col min="12" max="12" width="17.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.3984375" style="11"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="11"/>
+    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="11"/>
+    <col min="12" max="12" width="17.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.25" thickBot="1">
+    <row r="2" spans="1:14" ht="18" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -7013,7 +7013,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>70</v>
@@ -7046,7 +7046,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.15">
+    <row r="4" spans="1:14" ht="12.75">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -7071,7 +7071,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.15">
+    <row r="5" spans="1:14" ht="12.75">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
         <v>72</v>
@@ -7098,7 +7098,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.15">
+    <row r="6" spans="1:14" ht="12.75">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
         <v>73</v>
@@ -7119,7 +7119,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.15">
+    <row r="7" spans="1:14" ht="12.75">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
         <v>74</v>
@@ -7140,7 +7140,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.15">
+    <row r="8" spans="1:14" ht="12.75">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
         <v>75</v>
@@ -7167,7 +7167,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.15">
+    <row r="9" spans="1:14" ht="12.75">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
         <v>76</v>
@@ -7194,7 +7194,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.15">
+    <row r="10" spans="1:14" ht="12.75">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
         <v>78</v>
@@ -7221,7 +7221,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.15">
+    <row r="11" spans="1:14" ht="12.75">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
@@ -7248,7 +7248,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.15">
+    <row r="12" spans="1:14" ht="12.75">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
         <v>82</v>
@@ -7275,7 +7275,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.15">
+    <row r="13" spans="1:14" ht="12.75">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
         <v>85</v>
@@ -7302,7 +7302,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.15">
+    <row r="14" spans="1:14" ht="12.75">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
         <v>87</v>
@@ -7329,7 +7329,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.15">
+    <row r="15" spans="1:14" ht="12.75">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>90</v>
@@ -7356,7 +7356,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.15">
+    <row r="16" spans="1:14" ht="12.75">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
         <v>93</v>
@@ -7383,7 +7383,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.15">
+    <row r="17" spans="1:14" ht="12.75">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
         <v>95</v>
@@ -7410,7 +7410,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.15">
+    <row r="18" spans="1:14" ht="12.75">
       <c r="B18" s="19" t="s">
         <v>97</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.15">
+    <row r="19" spans="1:14" ht="12.75">
       <c r="B19" s="19" t="s">
         <v>99</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.15">
+    <row r="20" spans="1:14" ht="12.75">
       <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
@@ -7488,7 +7488,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.15">
+    <row r="21" spans="1:14" ht="12.75">
       <c r="B21" s="19" t="s">
         <v>103</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.15">
+    <row r="22" spans="1:14" ht="12.75">
       <c r="B22" s="19" t="s">
         <v>106</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.15">
+    <row r="23" spans="1:14" ht="12.75">
       <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.15">
+    <row r="24" spans="1:14" ht="12.75">
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.15">
+    <row r="25" spans="1:14" ht="12.75">
       <c r="B25" s="19" t="s">
         <v>114</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.15">
+    <row r="26" spans="1:14" ht="12.75">
       <c r="B26" s="19" t="s">
         <v>116</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.15">
+    <row r="27" spans="1:14" ht="12.75">
       <c r="B27" s="19" t="s">
         <v>118</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.15">
+    <row r="28" spans="1:14" ht="12.75">
       <c r="B28" s="19" t="s">
         <v>121</v>
       </c>
@@ -7669,7 +7669,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.15">
+    <row r="29" spans="1:14" ht="12.75">
       <c r="B29" s="19" t="s">
         <v>123</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.15">
+    <row r="30" spans="1:14" ht="12.75">
       <c r="B30" s="19" t="s">
         <v>124</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.15">
+    <row r="31" spans="1:14" ht="12.75">
       <c r="B31" s="19" t="s">
         <v>126</v>
       </c>
@@ -7720,7 +7720,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.15">
+    <row r="32" spans="1:14" ht="12.75">
       <c r="B32" s="19" t="s">
         <v>128</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.15">
+    <row r="33" spans="2:9" ht="12.75">
       <c r="B33" s="19" t="s">
         <v>130</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.15">
+    <row r="34" spans="2:9" ht="12.75">
       <c r="B34" s="19" t="s">
         <v>132</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.15">
+    <row r="35" spans="2:9" ht="12.75">
       <c r="B35" s="19" t="s">
         <v>133</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.15">
+    <row r="36" spans="2:9" ht="12.75">
       <c r="B36" s="19" t="s">
         <v>134</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.15">
+    <row r="37" spans="2:9" ht="12.75">
       <c r="B37" s="19" t="s">
         <v>135</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.15">
+    <row r="38" spans="2:9" ht="12.75">
       <c r="B38" s="19" t="s">
         <v>136</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.15">
+    <row r="39" spans="2:9" ht="12.75">
       <c r="B39" s="19" t="s">
         <v>137</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.15">
+    <row r="40" spans="2:9" ht="12.75">
       <c r="B40" s="19" t="s">
         <v>138</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.15">
+    <row r="41" spans="2:9" ht="12.75">
       <c r="B41" s="19" t="s">
         <v>139</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13.15">
+    <row r="42" spans="2:9" ht="12.75">
       <c r="B42" s="19" t="s">
         <v>140</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13.15">
+    <row r="43" spans="2:9" ht="12.75">
       <c r="B43" s="19" t="s">
         <v>141</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13.15">
+    <row r="44" spans="2:9" ht="12.75">
       <c r="B44" s="19" t="s">
         <v>142</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13.15">
+    <row r="45" spans="2:9" ht="12.75">
       <c r="B45" s="19" t="s">
         <v>143</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13.15">
+    <row r="46" spans="2:9" ht="12.75">
       <c r="B46" s="19" t="s">
         <v>144</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13.15">
+    <row r="47" spans="2:9" ht="12.75">
       <c r="B47" s="19" t="s">
         <v>145</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13.15">
+    <row r="48" spans="2:9" ht="12.75">
       <c r="B48" s="19" t="s">
         <v>146</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.15">
+    <row r="49" spans="2:9" ht="12.75">
       <c r="B49" s="19" t="s">
         <v>147</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.15">
+    <row r="50" spans="2:9" ht="12.75">
       <c r="B50" s="19" t="s">
         <v>148</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.15">
+    <row r="51" spans="2:9" ht="12.75">
       <c r="B51" s="19" t="s">
         <v>149</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.15">
+    <row r="52" spans="2:9" ht="12.75">
       <c r="B52" s="19" t="s">
         <v>150</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.15">
+    <row r="53" spans="2:9" ht="12.75">
       <c r="B53" s="19" t="s">
         <v>151</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13.15">
+    <row r="54" spans="2:9" ht="12.75">
       <c r="B54" s="19" t="s">
         <v>152</v>
       </c>
@@ -8557,12 +8557,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.25" thickBot="1">
+    <row r="99" spans="5:10" ht="18" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
         <v>49</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="14.25">
+    <row r="101" spans="5:10" ht="15">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
         <v>189</v>
@@ -8598,7 +8598,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="14.25">
+    <row r="102" spans="5:10" ht="15">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
         <v>191</v>
@@ -8621,19 +8621,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="8.86328125" style="6"/>
-    <col min="3" max="3" width="20.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.86328125" style="6"/>
+    <col min="1" max="2" width="8.85546875" style="6"/>
+    <col min="3" max="3" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.25" thickBot="1">
+    <row r="3" spans="2:4" ht="18" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>51</v>
       </c>
@@ -8825,12 +8825,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.25" thickBot="1">
+    <row r="25" spans="2:4" ht="18" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
         <v>172</v>
       </c>
